--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.0246941623531</v>
+        <v>10.56651280138238</v>
       </c>
       <c r="D2" t="n">
-        <v>65.05851654497415</v>
+        <v>10.5720089385583</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F2" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.4278289867736</v>
+        <v>10.14452221035071</v>
       </c>
       <c r="D3" t="n">
-        <v>62.38926650007662</v>
+        <v>10.13825580626245</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F3" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.45055689622765</v>
+        <v>7.548215495636994</v>
       </c>
       <c r="D4" t="n">
-        <v>46.41769465255747</v>
+        <v>7.54287538104059</v>
       </c>
       <c r="E4" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F4" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.07572396514213</v>
+        <v>6.349805144335597</v>
       </c>
       <c r="D5" t="n">
-        <v>39.18795297073682</v>
+        <v>6.368042357744732</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F5" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.84678230924328</v>
+        <v>8.912602125252034</v>
       </c>
       <c r="D6" t="n">
-        <v>54.62887799260164</v>
+        <v>8.877192673797767</v>
       </c>
       <c r="E6" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F6" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.91033523332884</v>
+        <v>4.372929475415937</v>
       </c>
       <c r="D7" t="n">
-        <v>26.63957865634956</v>
+        <v>4.328931531656804</v>
       </c>
       <c r="E7" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F7" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.64268450804749</v>
+        <v>5.141936232557718</v>
       </c>
       <c r="D8" t="n">
-        <v>31.97566574301311</v>
+        <v>5.196045683239631</v>
       </c>
       <c r="E8" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F8" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.52422858136195</v>
+        <v>4.472687144471317</v>
       </c>
       <c r="D9" t="n">
-        <v>27.82929928695107</v>
+        <v>4.522261134129549</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F9" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.8249936587045</v>
+        <v>3.546561469539481</v>
       </c>
       <c r="D10" t="n">
-        <v>21.57046677161201</v>
+        <v>3.505200850386951</v>
       </c>
       <c r="E10" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F10" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.34488016733462</v>
+        <v>9.968543027191876</v>
       </c>
       <c r="D11" t="n">
-        <v>61.63950416609141</v>
+        <v>10.01641942698985</v>
       </c>
       <c r="E11" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F11" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.00868225995132</v>
+        <v>6.66391086724209</v>
       </c>
       <c r="D12" t="n">
-        <v>40.98461738423163</v>
+        <v>6.66000032493764</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F12" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50.5791449666285</v>
+        <v>8.219111057077132</v>
       </c>
       <c r="D13" t="n">
-        <v>50.83866917833168</v>
+        <v>8.261283741478898</v>
       </c>
       <c r="E13" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F13" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.70654593277411</v>
+        <v>5.639813714075793</v>
       </c>
       <c r="D14" t="n">
-        <v>34.80412478118221</v>
+        <v>5.655670276942109</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F14" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.05948228148039</v>
+        <v>7.322165870740564</v>
       </c>
       <c r="D15" t="n">
-        <v>44.95637574322839</v>
+        <v>7.305411058274614</v>
       </c>
       <c r="E15" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F15" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.91797801918749</v>
+        <v>5.999171428117968</v>
       </c>
       <c r="D16" t="n">
-        <v>36.60056594822453</v>
+        <v>5.947591966586487</v>
       </c>
       <c r="E16" t="n">
-        <v>13.2006966702231</v>
+        <v>2.145113208911254</v>
       </c>
       <c r="F16" t="n">
-        <v>13.2348312638714</v>
+        <v>2.150660080379103</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
